--- a/saha_durum_operasyon_tablosu.xlsx
+++ b/saha_durum_operasyon_tablosu.xlsx
@@ -1,17 +1,36 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acevizci\Desktop\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65413923-3649-4549-B2F1-8E5EDEAA9837}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Saha Durum" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Saha Durum" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -22,111 +41,107 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="32">
   <si>
-    <t xml:space="preserve">Saha Durum ve Operasyon Detay Tablosu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toplam CİK Sayısı</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Üretilen Toplam Kabin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Üretilen Toplam MMC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devreye Alınan Kurum Sayısı</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ağustos ayında Üretilen Toplam Kabin</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ağustos ayında Üretilen Toplam MMC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aşama / Durum</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CİK Sayısı</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kabin Sayısı</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MMC Sayısı</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Açıklama ve Operasyonel Not</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keşif Bekleyen</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Saha keşif çalışmaları planlanmış olup erişim ve fizibilite onayları beklenmektedir.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Altyapı Planlanan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Keşfi tamamlanan lokasyonlarda kablolama ve mimari hazırlık süreci başlatılmıştır.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Altyapı Devam Eden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Şu an aktif olarak devam eden altyapı kazı/montaj çalışması bulunmamaktadır.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Altyapı Tamamlanan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiziki altyapısı eksiksiz bitirilip kabin montajına hazır hale getirilen lokasyonlar.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sevkiyat Yapılan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fabrika üretiminden çıkıp ilgili kurumlara nakliyesi gerçekleştirilen donanımlar.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kurulumu Devam Eden</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sahada montaj, kablolama ve ilk bağlantı testleri sürdürülen tesisler.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kurulumu Tamamlanan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sahada montaj, kablolama, ilk bağlantı testleri tamamlanan tesisler.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Devreye Alınan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tüm kabul testleri başarıyla geçip canlı operasyona alınan nihai sistemler.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toplam</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toplam 94 CİK ve 3000 MMC Devreye alım planı vardır.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">*Bir kurum sevkiyat planında onunla beraber 94 kurum mevcut.</t>
+    <t>Saha Durum ve Operasyon Detay Tablosu</t>
+  </si>
+  <si>
+    <t>Toplam CİK Sayısı</t>
+  </si>
+  <si>
+    <t>Üretilen Toplam Kabin</t>
+  </si>
+  <si>
+    <t>Üretilen Toplam MMC</t>
+  </si>
+  <si>
+    <t>Devreye Alınan Kurum Sayısı</t>
+  </si>
+  <si>
+    <t>Ağustos ayında Üretilen Toplam Kabin</t>
+  </si>
+  <si>
+    <t>Ağustos ayında Üretilen Toplam MMC</t>
+  </si>
+  <si>
+    <t>Aşama / Durum</t>
+  </si>
+  <si>
+    <t>CİK Sayısı</t>
+  </si>
+  <si>
+    <t>Kabin Sayısı</t>
+  </si>
+  <si>
+    <t>MMC Sayısı</t>
+  </si>
+  <si>
+    <t>Açıklama ve Operasyonel Not</t>
+  </si>
+  <si>
+    <t>Keşif Bekleyen</t>
+  </si>
+  <si>
+    <t>Saha keşif çalışmaları planlanmış olup erişim ve fizibilite onayları beklenmektedir.</t>
+  </si>
+  <si>
+    <t>Altyapı Planlanan</t>
+  </si>
+  <si>
+    <t>Keşfi tamamlanan lokasyonlarda kablolama ve mimari hazırlık süreci başlatılmıştır.</t>
+  </si>
+  <si>
+    <t>Altyapı Devam Eden</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Şu an aktif olarak devam eden altyapı kazı/montaj çalışması bulunmamaktadır.</t>
+  </si>
+  <si>
+    <t>Altyapı Tamamlanan</t>
+  </si>
+  <si>
+    <t>Fiziki altyapısı eksiksiz bitirilip kabin montajına hazır hale getirilen lokasyonlar.</t>
+  </si>
+  <si>
+    <t>Sevkiyat Yapılan</t>
+  </si>
+  <si>
+    <t>Fabrika üretiminden çıkıp ilgili kurumlara nakliyesi gerçekleştirilen donanımlar.</t>
+  </si>
+  <si>
+    <t>Kurulumu Devam Eden</t>
+  </si>
+  <si>
+    <t>Sahada montaj, kablolama ve ilk bağlantı testleri sürdürülen tesisler.</t>
+  </si>
+  <si>
+    <t>Kurulumu Tamamlanan</t>
+  </si>
+  <si>
+    <t>Sahada montaj, kablolama, ilk bağlantı testleri tamamlanan tesisler.</t>
+  </si>
+  <si>
+    <t>Devreye Alınan</t>
+  </si>
+  <si>
+    <t>Tüm kabul testleri başarıyla geçip canlı operasyona alınan nihai sistemler.</t>
+  </si>
+  <si>
+    <t>Toplam</t>
+  </si>
+  <si>
+    <t>Toplam 94 CİK ve 3000 MMC Devreye alım planı vardır.</t>
+  </si>
+  <si>
+    <t>*Bir kurum sevkiyat planında onunla beraber 94 kurum mevcut.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="General"/>
-  </numFmts>
-  <fonts count="13">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -135,82 +150,58 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="14"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF555555"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
       <sz val="16"/>
       <color rgb="FF2E5396"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <i val="true"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i/>
       <sz val="9"/>
       <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <i val="true"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i/>
       <sz val="8"/>
       <color rgb="FF666666"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -241,14 +232,14 @@
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FFBFBFBF"/>
       </left>
@@ -264,85 +255,41 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="11">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -401,47 +348,63 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF2E5396"/>
       <rgbColor rgb="FF555555"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -449,12 +412,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -483,7 +446,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -504,7 +467,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -555,7 +518,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -573,257 +536,256 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E21"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="55"/>
+    <col min="1" max="1" width="22" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="5" max="5" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="n">
+    <row r="4" spans="1:5" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A4" s="2">
         <v>94</v>
       </c>
-      <c r="B4" s="3" t="n">
+      <c r="B4" s="2">
         <v>1713</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="C4" s="2">
         <v>1612</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="n">
+    <row r="7" spans="1:5" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="n">
+      <c r="B7" s="2">
         <v>937</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="C7" s="2">
         <v>722</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="4" t="s">
+    <row r="10" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="3" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
+    <row r="11" spans="1:5" ht="24" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B11" s="5" t="n">
+      <c r="B11" s="4">
         <v>2</v>
       </c>
-      <c r="C11" s="5" t="n">
+      <c r="C11" s="4">
         <v>84</v>
       </c>
-      <c r="D11" s="5" t="n">
+      <c r="D11" s="4">
         <v>86</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="5" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
+    <row r="12" spans="1:5" ht="24" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="B12" s="5" t="n">
+      <c r="B12" s="4">
         <v>19</v>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="C12" s="4">
         <v>523</v>
       </c>
-      <c r="D12" s="5" t="n">
+      <c r="D12" s="4">
         <v>540</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="5" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="s">
+    <row r="13" spans="1:5" ht="24" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="5" t="s">
+      <c r="B13" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="5" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="5" t="s">
+    <row r="14" spans="1:5" ht="24" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="5" t="n">
+      <c r="B14" s="4">
         <v>31</v>
       </c>
-      <c r="C14" s="5" t="n">
+      <c r="C14" s="4">
         <v>955</v>
       </c>
-      <c r="D14" s="5" t="n">
+      <c r="D14" s="4">
         <v>985</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="s">
+    <row r="15" spans="1:5" ht="24" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="5" t="n">
+      <c r="B15" s="4">
         <v>8</v>
       </c>
-      <c r="C15" s="5" t="n">
+      <c r="C15" s="4">
         <v>261</v>
       </c>
-      <c r="D15" s="5" t="n">
+      <c r="D15" s="4">
         <v>269</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="5" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="s">
+    <row r="16" spans="1:5" ht="24" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B16" s="5" t="n">
+      <c r="B16" s="4">
         <v>27</v>
       </c>
-      <c r="C16" s="5" t="n">
+      <c r="C16" s="4">
         <v>950</v>
       </c>
-      <c r="D16" s="5" t="n">
+      <c r="D16" s="4">
         <v>976</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="5" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="s">
+    <row r="17" spans="1:5" ht="24" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="B17" s="5" t="n">
+      <c r="B17" s="4">
         <v>0</v>
       </c>
-      <c r="C17" s="5" t="n">
+      <c r="C17" s="4">
         <v>0</v>
       </c>
-      <c r="D17" s="5" t="n">
+      <c r="D17" s="4">
         <v>0</v>
       </c>
-      <c r="E17" s="6" t="s">
+      <c r="E17" s="5" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="s">
+    <row r="18" spans="1:5" ht="24" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B18" s="5" t="n">
+      <c r="B18" s="4">
         <v>6</v>
       </c>
-      <c r="C18" s="5" t="n">
+      <c r="C18" s="4">
         <v>138</v>
       </c>
-      <c r="D18" s="5" t="n">
+      <c r="D18" s="4">
         <v>143</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="E18" s="5" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="B19" s="8" t="n">
-        <f aca="false">SUM(B11:B18)</f>
+      <c r="B19" s="7">
+        <f>SUM(B11:B18)</f>
         <v>93</v>
       </c>
-      <c r="C19" s="8" t="n">
-        <f aca="false">SUM(C11:C18)</f>
+      <c r="C19" s="7">
+        <f>SUM(C11:C18)</f>
         <v>2911</v>
       </c>
-      <c r="D19" s="8" t="n">
-        <f aca="false">SUM(D11:D18)</f>
+      <c r="D19" s="7">
+        <f>SUM(D11:D18)</f>
         <v>2999</v>
       </c>
-      <c r="E19" s="9" t="s">
+      <c r="E19" s="8" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="10" t="s">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" s="9" t="s">
         <v>31</v>
       </c>
     </row>
@@ -831,12 +793,7 @@
   <mergeCells count="1">
     <mergeCell ref="A1:E1"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/saha_durum_operasyon_tablosu.xlsx
+++ b/saha_durum_operasyon_tablosu.xlsx
@@ -1,33 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\acevizci\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sdursun\Desktop\YÖNETİM PROJE TAKİP RAPOR\02.1 Ağustos 2026 Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65413923-3649-4549-B2F1-8E5EDEAA9837}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C3B9422-3A13-43B5-B53E-78BFA59DC929}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13920" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Saha Durum" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
     </ext>
@@ -583,10 +572,10 @@
         <v>94</v>
       </c>
       <c r="B4" s="2">
-        <v>1713</v>
+        <v>1703</v>
       </c>
       <c r="C4" s="2">
-        <v>1612</v>
+        <v>1638</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -602,7 +591,7 @@
     </row>
     <row r="7" spans="1:5" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B7" s="2">
         <v>937</v>
@@ -650,13 +639,13 @@
         <v>14</v>
       </c>
       <c r="B12" s="4">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="C12" s="4">
-        <v>523</v>
+        <v>459</v>
       </c>
       <c r="D12" s="4">
-        <v>540</v>
+        <v>474</v>
       </c>
       <c r="E12" s="5" t="s">
         <v>15</v>
@@ -684,13 +673,13 @@
         <v>19</v>
       </c>
       <c r="B14" s="4">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C14" s="4">
-        <v>955</v>
+        <v>803</v>
       </c>
       <c r="D14" s="4">
-        <v>985</v>
+        <v>827</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>20</v>
@@ -701,13 +690,13 @@
         <v>21</v>
       </c>
       <c r="B15" s="4">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C15" s="4">
-        <v>261</v>
+        <v>397</v>
       </c>
       <c r="D15" s="4">
-        <v>269</v>
+        <v>412</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>22</v>
@@ -718,13 +707,13 @@
         <v>23</v>
       </c>
       <c r="B16" s="4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C16" s="4">
-        <v>950</v>
+        <v>974</v>
       </c>
       <c r="D16" s="4">
-        <v>976</v>
+        <v>1001</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>24</v>
@@ -752,13 +741,13 @@
         <v>27</v>
       </c>
       <c r="B18" s="4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C18" s="4">
-        <v>138</v>
+        <v>194</v>
       </c>
       <c r="D18" s="4">
-        <v>143</v>
+        <v>200</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>28</v>
@@ -770,7 +759,7 @@
       </c>
       <c r="B19" s="7">
         <f>SUM(B11:B18)</f>
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C19" s="7">
         <f>SUM(C11:C18)</f>
@@ -778,7 +767,7 @@
       </c>
       <c r="D19" s="7">
         <f>SUM(D11:D18)</f>
-        <v>2999</v>
+        <v>3000</v>
       </c>
       <c r="E19" s="8" t="s">
         <v>30</v>
@@ -794,6 +783,233 @@
     <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="de48f57a-7a98-42ae-8400-a2fbfcb9b9a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100EB4C2675C53E6A4DB1D8BC8AD034CCC1" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="604af05efb6f7a4fa4d9b65a9922e243">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="de48f57a-7a98-42ae-8400-a2fbfcb9b9a5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0386dbcb163751ea84dc3c1f3a1ba8df" ns2:_="">
+    <xsd:import namespace="de48f57a-7a98-42ae-8400-a2fbfcb9b9a5"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="de48f57a-7a98-42ae-8400-a2fbfcb9b9a5" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="7b1e589d-88e8-49d4-851b-d1cb70381577" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="14" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{90551FEF-EEB5-4761-9E89-2DE4B617EEEF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="de48f57a-7a98-42ae-8400-a2fbfcb9b9a5"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F8AA350-7ECB-412F-AC7B-16317C5370E9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB51F81E-0EA4-4AE0-BD9A-239FA574BD6B}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="de48f57a-7a98-42ae-8400-a2fbfcb9b9a5"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/saha_durum_operasyon_tablosu.xlsx
+++ b/saha_durum_operasyon_tablosu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sdursun\Desktop\YÖNETİM PROJE TAKİP RAPOR\02.1 Ağustos 2026 Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C3B9422-3A13-43B5-B53E-78BFA59DC929}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82EFB7F5-1E0C-4F99-BA5D-811BB45FF4A9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13920" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -541,8 +541,8 @@
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="13" customWidth="1"/>
+    <col min="2" max="2" width="31.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="55" customWidth="1"/>
   </cols>
@@ -572,7 +572,7 @@
         <v>94</v>
       </c>
       <c r="B4" s="2">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="C4" s="2">
         <v>1638</v>
@@ -798,15 +798,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100EB4C2675C53E6A4DB1D8BC8AD034CCC1" ma:contentTypeVersion="9" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="604af05efb6f7a4fa4d9b65a9922e243">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="de48f57a-7a98-42ae-8400-a2fbfcb9b9a5" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0386dbcb163751ea84dc3c1f3a1ba8df" ns2:_="">
     <xsd:import namespace="de48f57a-7a98-42ae-8400-a2fbfcb9b9a5"/>
@@ -978,6 +969,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{90551FEF-EEB5-4761-9E89-2DE4B617EEEF}">
   <ds:schemaRefs>
@@ -989,14 +989,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F8AA350-7ECB-412F-AC7B-16317C5370E9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BB51F81E-0EA4-4AE0-BD9A-239FA574BD6B}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1012,4 +1004,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9F8AA350-7ECB-412F-AC7B-16317C5370E9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/saha_durum_operasyon_tablosu.xlsx
+++ b/saha_durum_operasyon_tablosu.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sdursun\Desktop\YÖNETİM PROJE TAKİP RAPOR\02.1 Ağustos 2026 Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82EFB7F5-1E0C-4F99-BA5D-811BB45FF4A9}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B681EC2-F82C-4C71-A68F-AFEE20DA1A3F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13920" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -572,7 +572,7 @@
         <v>94</v>
       </c>
       <c r="B4" s="2">
-        <v>1704</v>
+        <v>1703</v>
       </c>
       <c r="C4" s="2">
         <v>1638</v>

--- a/saha_durum_operasyon_tablosu.xlsx
+++ b/saha_durum_operasyon_tablosu.xlsx
@@ -5,17 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sdursun\Desktop\YÖNETİM PROJE TAKİP RAPOR\02.1 Ağustos 2026 Dashboard\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sdursun\Desktop\YÖNETİM PROJE TAKİP RAPOR\03.1-Eylül 2026 Dashboard\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B681EC2-F82C-4C71-A68F-AFEE20DA1A3F}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5874BBF-2343-416A-B5F3-5CA8B74E6CFB}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13920" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="17520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Saha Durum" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
       <xlwcv:version setVersion="1"/>
@@ -45,12 +45,6 @@
     <t>Devreye Alınan Kurum Sayısı</t>
   </si>
   <si>
-    <t>Ağustos ayında Üretilen Toplam Kabin</t>
-  </si>
-  <si>
-    <t>Ağustos ayında Üretilen Toplam MMC</t>
-  </si>
-  <si>
     <t>Aşama / Durum</t>
   </si>
   <si>
@@ -124,6 +118,12 @@
   </si>
   <si>
     <t>*Bir kurum sevkiyat planında onunla beraber 94 kurum mevcut.</t>
+  </si>
+  <si>
+    <t>Eylül ayında Üretilen Toplam Kabin</t>
+  </si>
+  <si>
+    <t>Eylül ayında Üretilen Toplam MMC</t>
   </si>
 </sst>
 </file>
@@ -572,10 +572,10 @@
         <v>94</v>
       </c>
       <c r="B4" s="2">
-        <v>1703</v>
+        <v>2003</v>
       </c>
       <c r="C4" s="2">
-        <v>1638</v>
+        <v>1918</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -583,43 +583,43 @@
         <v>4</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>6</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="20.25" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="B7" s="2">
-        <v>937</v>
+        <v>300</v>
       </c>
       <c r="C7" s="2">
-        <v>722</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="D10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="E10" s="3" t="s">
         <v>9</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="24" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B11" s="4">
         <v>2</v>
@@ -631,131 +631,131 @@
         <v>86</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="24" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12" s="4">
         <v>14</v>
       </c>
-      <c r="B12" s="4">
-        <v>15</v>
-      </c>
       <c r="C12" s="4">
-        <v>459</v>
+        <v>410</v>
       </c>
       <c r="D12" s="4">
-        <v>474</v>
+        <v>424</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="24" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="E13" s="5" t="s">
         <v>16</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="24" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B14" s="4">
         <v>25</v>
       </c>
       <c r="C14" s="4">
-        <v>803</v>
+        <v>818</v>
       </c>
       <c r="D14" s="4">
-        <v>827</v>
+        <v>842</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="24" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B15" s="4">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C15" s="4">
-        <v>397</v>
+        <v>430</v>
       </c>
       <c r="D15" s="4">
-        <v>412</v>
+        <v>444</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="24" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B16" s="4">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C16" s="4">
-        <v>974</v>
+        <v>870</v>
       </c>
       <c r="D16" s="4">
-        <v>1001</v>
+        <v>895</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="24" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B17" s="4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C17" s="4">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="D17" s="4">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="24" x14ac:dyDescent="0.25">
       <c r="A18" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="B18" s="4">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C18" s="4">
-        <v>194</v>
+        <v>224</v>
       </c>
       <c r="D18" s="4">
-        <v>200</v>
+        <v>233</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="B19" s="7">
         <f>SUM(B11:B18)</f>
@@ -770,12 +770,12 @@
         <v>3000</v>
       </c>
       <c r="E19" s="8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="9" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
